--- a/output/laminas_comunales/comunal_s_isapre_a_2022_maule.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2022_maule.xlsx
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>31088</v>
+        <v>13.05834418448356</v>
       </c>
     </row>
     <row r="3">
@@ -399,157 +399,157 @@
         </is>
       </c>
       <c r="C3">
-        <v>19483</v>
+        <v>11.48017205821696</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="C4">
-        <v>8379</v>
+        <v>8.528764238537379</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C5">
-        <v>4455</v>
+        <v>8.084244323828454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="C6">
-        <v>4230</v>
+        <v>7.749650854135644</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="C7">
-        <v>2722</v>
+        <v>7.326785240244226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C8">
-        <v>2405</v>
+        <v>7.277296271603672</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Molina</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="C9">
-        <v>2397</v>
+        <v>6.734578381437465</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Vichuquén</t>
         </is>
       </c>
       <c r="C10">
-        <v>2208</v>
+        <v>6.378514477549308</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="C11">
-        <v>1954</v>
+        <v>5.592652709005362</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="C12">
-        <v>1494</v>
+        <v>5.292265150933251</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Pelluhue</t>
         </is>
       </c>
       <c r="C13">
-        <v>1419</v>
+        <v>5.134899912967798</v>
       </c>
     </row>
     <row r="14">
@@ -564,247 +564,247 @@
         </is>
       </c>
       <c r="C14">
-        <v>1053</v>
+        <v>5.09433962264151</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C15">
-        <v>944</v>
+        <v>4.763702849874797</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="C16">
-        <v>937</v>
+        <v>4.725604934366598</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Rauco</t>
         </is>
       </c>
       <c r="C17">
-        <v>730</v>
+        <v>4.723430702299565</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="C18">
-        <v>714</v>
+        <v>4.692979659503921</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="C19">
-        <v>689</v>
+        <v>4.686464788183484</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="C20">
-        <v>641</v>
+        <v>4.482699846599625</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="C21">
-        <v>617</v>
+        <v>4.372379567040301</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7103</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="C22">
-        <v>552</v>
+        <v>4.125243891108427</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rauco</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="C23">
-        <v>532</v>
+        <v>4.035601746918016</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="C24">
-        <v>532</v>
+        <v>3.979714454469541</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
+          <t>Colbún</t>
         </is>
       </c>
       <c r="C25">
-        <v>531</v>
+        <v>3.837175969531922</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="C26">
-        <v>526</v>
+        <v>3.772546621828187</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7202</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Chanco</t>
         </is>
       </c>
       <c r="C27">
-        <v>511</v>
+        <v>3.143357724415129</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Retiro</t>
         </is>
       </c>
       <c r="C28">
-        <v>444</v>
+        <v>2.871992472781038</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="C29">
-        <v>305</v>
+        <v>2.707103602686749</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="C30">
-        <v>304</v>
+        <v>2.579023577302407</v>
       </c>
     </row>
     <row r="31">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>95</v>
+        <v>2.385735811150176</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
